--- a/results/res_multidro.xlsx
+++ b/results/res_multidro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\GDOforecast\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C865DC-4970-432A-A13B-8141A5C40AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0360E767-E1F9-4780-A3C7-F2A1AF9FD957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="936" yWindow="636" windowWidth="20388" windowHeight="13644" xr2:uid="{C9FFD5E3-00FD-495A-B5B0-4F4E6F374C6B}"/>
+    <workbookView xWindow="3105" yWindow="420" windowWidth="24360" windowHeight="14385" xr2:uid="{C9FFD5E3-00FD-495A-B5B0-4F4E6F374C6B}"/>
   </bookViews>
   <sheets>
     <sheet name="res_multidro" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="10">
   <si>
     <t>Instance</t>
   </si>
@@ -64,12 +62,15 @@
   <si>
     <t>zeta</t>
   </si>
+  <si>
+    <t>Zfix</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -955,13 +956,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FA6DF6-3634-471C-8CDC-F38FCBC1D04C}">
-  <dimension ref="A1:L78"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M78"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="9" max="9" width="8.796875" style="2"/>
+    <col min="8" max="8" width="9" style="2"/>
+    <col min="10" max="10" width="8.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -983,23 +985,26 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1013,35 +1018,38 @@
         <v>20487</v>
       </c>
       <c r="E2">
-        <f>ROUND( $H2*J$3+J$2,0)</f>
+        <f>ROUND( $H2*K$3+K$2,0)</f>
         <v>19885</v>
       </c>
       <c r="F2">
-        <f t="shared" ref="F2:G16" si="0">ROUND( $H2*K$3+K$2,0)</f>
+        <f>ROUND( $H2*L$3+L$2,0)</f>
         <v>20492</v>
       </c>
       <c r="G2">
-        <f t="shared" si="0"/>
+        <f>ROUND( $H2*M$3+M$2,0)</f>
         <v>20478</v>
       </c>
-      <c r="H2">
-        <f>(D2-I$2)/I$3</f>
+      <c r="H2" s="2">
+        <f>(D2-J$2)/J$3</f>
         <v>-0.2490165143189591</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2">
+        <v>-0.2490165143189591</v>
+      </c>
+      <c r="J2" s="2">
         <v>20528.866666666665</v>
       </c>
-      <c r="J2" s="2">
+      <c r="K2" s="2">
         <v>19918</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <v>20535</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="2">
         <v>20515.933333333334</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1055,35 +1063,38 @@
         <v>20455</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E17" si="1">ROUND( $H3*J$3+J$2,0)</f>
+        <f t="shared" ref="E3:E16" si="0">ROUND( $H3*K$3+K$2,0)</f>
         <v>19860</v>
       </c>
       <c r="F3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F3:F16" si="1">ROUND( $H3*L$3+L$2,0)</f>
         <v>20459</v>
       </c>
       <c r="G3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G3:G16" si="2">ROUND( $H3*M$3+M$2,0)</f>
         <v>20449</v>
       </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H16" si="2">(D3-I$2)/I$3</f>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H16" si="3">(D3-J$2)/J$3</f>
         <v>-0.43934760806594192</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3">
+        <v>-0.43934760806594192</v>
+      </c>
+      <c r="J3" s="2">
         <v>168.12807287567679</v>
       </c>
-      <c r="J3" s="2">
+      <c r="K3" s="2">
         <v>132.11812896041178</v>
       </c>
-      <c r="K3" s="2">
+      <c r="L3" s="2">
         <v>173.9279544332461</v>
       </c>
-      <c r="L3" s="2">
+      <c r="M3" s="2">
         <v>151.9295743282247</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1097,23 +1108,26 @@
         <v>20766</v>
       </c>
       <c r="E4">
+        <f t="shared" si="0"/>
+        <v>20104</v>
+      </c>
+      <c r="F4">
         <f t="shared" si="1"/>
-        <v>20104</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
         <v>20780</v>
       </c>
       <c r="G4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20730</v>
       </c>
-      <c r="H4">
-        <f t="shared" si="2"/>
+      <c r="H4" s="2">
+        <f t="shared" si="3"/>
         <v>1.4104327092875475</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <v>1.4104327092875475</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1127,23 +1141,26 @@
         <v>20595</v>
       </c>
       <c r="E5">
+        <f t="shared" si="0"/>
+        <v>19970</v>
+      </c>
+      <c r="F5">
         <f t="shared" si="1"/>
-        <v>19970</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
         <v>20603</v>
       </c>
       <c r="G5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20576</v>
       </c>
-      <c r="H5">
-        <f t="shared" si="2"/>
+      <c r="H5" s="2">
+        <f t="shared" si="3"/>
         <v>0.39335092707710795</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <v>0.39335092707710795</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1157,23 +1174,26 @@
         <v>20381</v>
       </c>
       <c r="E6">
+        <f t="shared" si="0"/>
+        <v>19802</v>
+      </c>
+      <c r="F6">
         <f t="shared" si="1"/>
-        <v>19802</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
         <v>20382</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20382</v>
       </c>
-      <c r="H6">
-        <f t="shared" si="2"/>
+      <c r="H6" s="2">
+        <f t="shared" si="3"/>
         <v>-0.87948826235583966</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <v>-0.87948826235583966</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1187,23 +1207,26 @@
         <v>20767</v>
       </c>
       <c r="E7">
+        <f t="shared" si="0"/>
+        <v>20105</v>
+      </c>
+      <c r="F7">
         <f t="shared" si="1"/>
-        <v>20105</v>
-      </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
         <v>20781</v>
       </c>
       <c r="G7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20731</v>
       </c>
-      <c r="H7">
-        <f t="shared" si="2"/>
+      <c r="H7" s="2">
+        <f t="shared" si="3"/>
         <v>1.4163805559671405</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <v>1.4163805559671405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1217,23 +1240,26 @@
         <v>20383</v>
       </c>
       <c r="E8">
+        <f t="shared" si="0"/>
+        <v>19803</v>
+      </c>
+      <c r="F8">
         <f t="shared" si="1"/>
-        <v>19803</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="0"/>
         <v>20384</v>
       </c>
       <c r="G8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20384</v>
       </c>
-      <c r="H8">
-        <f t="shared" si="2"/>
+      <c r="H8" s="2">
+        <f t="shared" si="3"/>
         <v>-0.86759256899665327</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <v>-0.86759256899665327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1247,23 +1273,26 @@
         <v>20576</v>
       </c>
       <c r="E9">
+        <f t="shared" si="0"/>
+        <v>19955</v>
+      </c>
+      <c r="F9">
         <f t="shared" si="1"/>
-        <v>19955</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
         <v>20584</v>
       </c>
       <c r="G9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20559</v>
       </c>
-      <c r="H9">
-        <f t="shared" si="2"/>
+      <c r="H9" s="2">
+        <f t="shared" si="3"/>
         <v>0.28034184016483688</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <v>0.28034184016483688</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1277,23 +1306,26 @@
         <v>20834</v>
       </c>
       <c r="E10">
+        <f t="shared" si="0"/>
+        <v>20158</v>
+      </c>
+      <c r="F10">
         <f t="shared" si="1"/>
-        <v>20158</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
         <v>20851</v>
       </c>
       <c r="G10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20792</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="2"/>
+      <c r="H10" s="2">
+        <f t="shared" si="3"/>
         <v>1.814886283499886</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <v>1.814886283499886</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1307,23 +1339,26 @@
         <v>20466</v>
       </c>
       <c r="E11">
+        <f t="shared" si="0"/>
+        <v>19869</v>
+      </c>
+      <c r="F11">
         <f t="shared" si="1"/>
-        <v>19869</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
         <v>20470</v>
       </c>
       <c r="G11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20459</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="2"/>
+      <c r="H11" s="2">
+        <f t="shared" si="3"/>
         <v>-0.37392129459041656</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <v>-0.37392129459041656</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1337,23 +1372,26 @@
         <v>20393</v>
       </c>
       <c r="E12">
+        <f t="shared" si="0"/>
+        <v>19811</v>
+      </c>
+      <c r="F12">
         <f t="shared" si="1"/>
-        <v>19811</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
         <v>20394</v>
       </c>
       <c r="G12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20393</v>
       </c>
-      <c r="H12">
-        <f t="shared" si="2"/>
+      <c r="H12" s="2">
+        <f t="shared" si="3"/>
         <v>-0.80811410220072111</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <v>-0.80811410220072111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1367,23 +1405,26 @@
         <v>20580</v>
       </c>
       <c r="E13">
+        <f t="shared" si="0"/>
+        <v>19958</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="1"/>
-        <v>19958</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
         <v>20588</v>
       </c>
       <c r="G13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20562</v>
       </c>
-      <c r="H13">
-        <f t="shared" si="2"/>
+      <c r="H13" s="2">
+        <f t="shared" si="3"/>
         <v>0.30413322688320976</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <v>0.30413322688320976</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1397,23 +1438,26 @@
         <v>20231</v>
       </c>
       <c r="E14">
+        <f t="shared" si="0"/>
+        <v>19684</v>
+      </c>
+      <c r="F14">
         <f t="shared" si="1"/>
-        <v>19684</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
         <v>20227</v>
       </c>
       <c r="G14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20247</v>
       </c>
-      <c r="H14">
-        <f t="shared" si="2"/>
+      <c r="H14" s="2">
+        <f t="shared" si="3"/>
         <v>-1.7716652642948216</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <v>-1.7716652642948216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1427,23 +1471,26 @@
         <v>20662</v>
       </c>
       <c r="E15">
+        <f t="shared" si="0"/>
+        <v>20023</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="1"/>
-        <v>20023</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
         <v>20673</v>
       </c>
       <c r="G15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20636</v>
       </c>
-      <c r="H15">
-        <f t="shared" si="2"/>
+      <c r="H15" s="2">
+        <f t="shared" si="3"/>
         <v>0.79185665460985322</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <v>0.79185665460985322</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="1" customFormat="1">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
@@ -1457,24 +1504,27 @@
         <v>20357</v>
       </c>
       <c r="E16">
+        <f t="shared" si="0"/>
+        <v>19783</v>
+      </c>
+      <c r="F16">
         <f t="shared" si="1"/>
-        <v>19783</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
         <v>20357</v>
       </c>
       <c r="G16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20361</v>
       </c>
-      <c r="H16">
-        <f t="shared" si="2"/>
+      <c r="H16" s="2">
+        <f t="shared" si="3"/>
         <v>-1.0222365826660769</v>
       </c>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <v>-1.0222365826660769</v>
+      </c>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1485,38 +1535,42 @@
         <v>0</v>
       </c>
       <c r="D17">
+        <f>ROUND( $I17*J$18+J$17,0)</f>
         <v>20414</v>
       </c>
       <c r="E17">
-        <f>ROUND( $H17*J$18+J$17,0)</f>
+        <f>ROUND( $H17*K$18+K$17,0)</f>
         <v>20119</v>
       </c>
       <c r="F17">
-        <f t="shared" ref="F17:G32" si="3">ROUND( $H17*K$18+K$17,0)</f>
+        <f>ROUND( $H17*L$18+L$17,0)</f>
         <v>20529</v>
       </c>
       <c r="G17">
-        <f t="shared" si="3"/>
+        <f>ROUND( $H17*M$18+M$17,0)</f>
         <v>20425</v>
       </c>
-      <c r="H17">
-        <f>(D17-I$17)/I$18</f>
+      <c r="H17" s="2">
+        <f>(D17-J$17)/J$18</f>
         <v>-0.73835535955742937</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17">
+        <v>-0.73835535955742937</v>
+      </c>
+      <c r="J17" s="2">
         <v>20555.36</v>
       </c>
-      <c r="J17" s="2">
+      <c r="K17" s="2">
         <v>20234</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="2">
         <v>20677.919999999998</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="2">
         <v>20560.080000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1527,38 +1581,42 @@
         <v>1</v>
       </c>
       <c r="D18">
+        <f t="shared" ref="D18:D41" si="4">ROUND( $I18*J$18+J$17,0)</f>
         <v>20624</v>
       </c>
       <c r="E18">
-        <f t="shared" ref="E18:E42" si="4">ROUND( $H18*J$18+J$17,0)</f>
+        <f t="shared" ref="E18:E41" si="5">ROUND( $H18*K$18+K$17,0)</f>
         <v>20290</v>
       </c>
       <c r="F18">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F18:F32" si="6">ROUND( $H18*L$18+L$17,0)</f>
         <v>20750</v>
       </c>
       <c r="G18">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="G18:G32" si="7">ROUND( $H18*M$18+M$17,0)</f>
         <v>20626</v>
       </c>
-      <c r="H18">
-        <f t="shared" ref="H18:H41" si="5">(D18-I$17)/I$18</f>
+      <c r="H18" s="2">
+        <f t="shared" ref="H18:H41" si="8">(D18-J$17)/J$18</f>
         <v>0.35852229683093739</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18">
+        <v>0.35852229683093739</v>
+      </c>
+      <c r="J18" s="2">
         <v>191.45252779736285</v>
       </c>
-      <c r="J18" s="2">
+      <c r="K18" s="2">
         <v>156.05665637838072</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <v>202.02037917002335</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
         <v>183.01255038931075</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1569,26 +1627,30 @@
         <v>2</v>
       </c>
       <c r="D19">
+        <f t="shared" si="4"/>
         <v>20716</v>
       </c>
       <c r="E19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20365</v>
       </c>
       <c r="F19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20847</v>
       </c>
       <c r="G19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20714</v>
       </c>
-      <c r="H19">
-        <f t="shared" si="5"/>
+      <c r="H19" s="2">
+        <f t="shared" si="8"/>
         <v>0.83905917486774573</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <v>0.83905917486774573</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1599,26 +1661,30 @@
         <v>3</v>
       </c>
       <c r="D20">
+        <f t="shared" si="4"/>
         <v>20304</v>
       </c>
       <c r="E20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20029</v>
       </c>
       <c r="F20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20413</v>
       </c>
       <c r="G20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20320</v>
       </c>
-      <c r="H20">
-        <f t="shared" si="5"/>
+      <c r="H20" s="2">
+        <f t="shared" si="8"/>
         <v>-1.3129103224275263</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <v>-1.3129103224275263</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1629,26 +1695,30 @@
         <v>4</v>
       </c>
       <c r="D21">
+        <f t="shared" si="4"/>
         <v>20471</v>
       </c>
       <c r="E21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20165</v>
       </c>
       <c r="F21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20589</v>
       </c>
       <c r="G21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20479</v>
       </c>
-      <c r="H21">
-        <f t="shared" si="5"/>
+      <c r="H21" s="2">
+        <f t="shared" si="8"/>
         <v>-0.44063142425201551</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <v>-0.44063142425201551</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1659,26 +1729,30 @@
         <v>5</v>
       </c>
       <c r="D22">
+        <f t="shared" si="4"/>
         <v>20814</v>
       </c>
       <c r="E22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20445</v>
       </c>
       <c r="F22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20951</v>
       </c>
       <c r="G22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20807</v>
       </c>
-      <c r="H22">
-        <f t="shared" si="5"/>
+      <c r="H22" s="2">
+        <f t="shared" si="8"/>
         <v>1.3509354145156502</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <v>1.3509354145156502</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1689,26 +1763,30 @@
         <v>6</v>
       </c>
       <c r="D23">
+        <f t="shared" si="4"/>
         <v>20262</v>
       </c>
       <c r="E23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19995</v>
       </c>
       <c r="F23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20368</v>
       </c>
       <c r="G23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20280</v>
       </c>
-      <c r="H23">
-        <f t="shared" si="5"/>
+      <c r="H23" s="2">
+        <f t="shared" si="8"/>
         <v>-1.5322858537051995</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <v>-1.5322858537051995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1719,26 +1797,30 @@
         <v>7</v>
       </c>
       <c r="D24">
+        <f t="shared" si="4"/>
         <v>20717</v>
       </c>
       <c r="E24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20366</v>
       </c>
       <c r="F24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20848</v>
       </c>
       <c r="G24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20715</v>
       </c>
-      <c r="H24">
-        <f t="shared" si="5"/>
+      <c r="H24" s="2">
+        <f t="shared" si="8"/>
         <v>0.84428240180292835</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <v>0.84428240180292835</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1749,26 +1831,30 @@
         <v>8</v>
       </c>
       <c r="D25">
+        <f t="shared" si="4"/>
         <v>21006</v>
       </c>
       <c r="E25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20601</v>
       </c>
       <c r="F25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>21153</v>
       </c>
       <c r="G25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20991</v>
       </c>
-      <c r="H25">
-        <f t="shared" si="5"/>
+      <c r="H25" s="2">
+        <f t="shared" si="8"/>
         <v>2.3537949860707283</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <v>2.3537949860707283</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1779,26 +1865,30 @@
         <v>9</v>
       </c>
       <c r="D26">
+        <f t="shared" si="4"/>
         <v>20755</v>
       </c>
       <c r="E26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20397</v>
       </c>
       <c r="F26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20889</v>
       </c>
       <c r="G26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20751</v>
       </c>
-      <c r="H26">
-        <f t="shared" si="5"/>
+      <c r="H26" s="2">
+        <f t="shared" si="8"/>
         <v>1.042765025339871</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <v>1.042765025339871</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -1809,26 +1899,30 @@
         <v>10</v>
       </c>
       <c r="D27">
+        <f t="shared" si="4"/>
         <v>20459</v>
       </c>
       <c r="E27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20155</v>
       </c>
       <c r="F27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20576</v>
       </c>
       <c r="G27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20468</v>
       </c>
-      <c r="H27">
-        <f t="shared" si="5"/>
+      <c r="H27" s="2">
+        <f t="shared" si="8"/>
         <v>-0.50331014747420788</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <v>-0.50331014747420788</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -1839,26 +1933,30 @@
         <v>11</v>
       </c>
       <c r="D28">
+        <f t="shared" si="4"/>
         <v>20549</v>
       </c>
       <c r="E28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20229</v>
       </c>
       <c r="F28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20671</v>
       </c>
       <c r="G28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20554</v>
       </c>
-      <c r="H28">
-        <f t="shared" si="5"/>
+      <c r="H28" s="2">
+        <f t="shared" si="8"/>
         <v>-3.3219723307765008E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I28">
+        <v>-3.3219723307765008E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -1869,26 +1967,30 @@
         <v>12</v>
       </c>
       <c r="D29">
+        <f t="shared" si="4"/>
         <v>20557</v>
       </c>
       <c r="E29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20235</v>
       </c>
       <c r="F29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20680</v>
       </c>
       <c r="G29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20562</v>
       </c>
-      <c r="H29">
-        <f t="shared" si="5"/>
+      <c r="H29" s="2">
+        <f t="shared" si="8"/>
         <v>8.5660921736965857E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I29">
+        <v>8.5660921736965857E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1899,26 +2001,30 @@
         <v>13</v>
       </c>
       <c r="D30">
+        <f t="shared" si="4"/>
         <v>20738</v>
       </c>
       <c r="E30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20383</v>
       </c>
       <c r="F30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20871</v>
       </c>
       <c r="G30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20735</v>
       </c>
-      <c r="H30">
-        <f t="shared" si="5"/>
+      <c r="H30" s="2">
+        <f t="shared" si="8"/>
         <v>0.9539701674417651</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I30">
+        <v>0.9539701674417651</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1929,26 +2035,30 @@
         <v>14</v>
       </c>
       <c r="D31">
+        <f t="shared" si="4"/>
         <v>20632</v>
       </c>
       <c r="E31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20296</v>
       </c>
       <c r="F31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20759</v>
       </c>
       <c r="G31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20633</v>
       </c>
-      <c r="H31">
-        <f t="shared" si="5"/>
+      <c r="H31" s="2">
+        <f t="shared" si="8"/>
         <v>0.40030811231239899</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I31">
+        <v>0.40030811231239899</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1959,26 +2069,30 @@
         <v>15</v>
       </c>
       <c r="D32">
+        <f t="shared" si="4"/>
         <v>20586</v>
       </c>
       <c r="E32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20259</v>
       </c>
       <c r="F32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>20710</v>
       </c>
       <c r="G32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20589</v>
       </c>
-      <c r="H32">
-        <f t="shared" si="5"/>
+      <c r="H32" s="2">
+        <f t="shared" si="8"/>
         <v>0.16003967329399485</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I32">
+        <v>0.16003967329399485</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1989,26 +2103,30 @@
         <v>16</v>
       </c>
       <c r="D33">
+        <f t="shared" si="4"/>
         <v>20330</v>
       </c>
       <c r="E33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20050</v>
       </c>
       <c r="F33">
-        <f t="shared" ref="F33:F41" si="6">ROUND( $H33*K$18+K$17,0)</f>
+        <f t="shared" ref="F33:F41" si="9">ROUND( $H33*L$18+L$17,0)</f>
         <v>20440</v>
       </c>
       <c r="G33">
-        <f t="shared" ref="G33:G41" si="7">ROUND( $H33*L$18+L$17,0)</f>
+        <f t="shared" ref="G33:G41" si="10">ROUND( $H33*M$18+M$17,0)</f>
         <v>20345</v>
       </c>
-      <c r="H33">
-        <f t="shared" si="5"/>
+      <c r="H33" s="2">
+        <f t="shared" si="8"/>
         <v>-1.1771064221127761</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I33">
+        <v>-1.1771064221127761</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -2019,26 +2137,30 @@
         <v>17</v>
       </c>
       <c r="D34">
+        <f t="shared" si="4"/>
         <v>20370</v>
       </c>
       <c r="E34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20083</v>
       </c>
       <c r="F34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>20482</v>
       </c>
       <c r="G34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20383</v>
       </c>
-      <c r="H34">
-        <f t="shared" si="5"/>
+      <c r="H34" s="2">
+        <f t="shared" si="8"/>
         <v>-0.96817734470546812</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I34">
+        <v>-0.96817734470546812</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -2049,26 +2171,30 @@
         <v>18</v>
       </c>
       <c r="D35">
+        <f t="shared" si="4"/>
         <v>20453</v>
       </c>
       <c r="E35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20151</v>
       </c>
       <c r="F35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>20570</v>
       </c>
       <c r="G35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20462</v>
       </c>
-      <c r="H35">
-        <f t="shared" si="5"/>
+      <c r="H35" s="2">
+        <f t="shared" si="8"/>
         <v>-0.53464950908530406</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I35">
+        <v>-0.53464950908530406</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -2079,26 +2205,30 @@
         <v>19</v>
       </c>
       <c r="D36">
+        <f t="shared" si="4"/>
         <v>20364</v>
       </c>
       <c r="E36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20078</v>
       </c>
       <c r="F36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>20476</v>
       </c>
       <c r="G36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20377</v>
       </c>
-      <c r="H36">
-        <f t="shared" si="5"/>
+      <c r="H36" s="2">
+        <f t="shared" si="8"/>
         <v>-0.99951670631656431</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I36">
+        <v>-0.99951670631656431</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -2109,26 +2239,30 @@
         <v>20</v>
       </c>
       <c r="D37">
+        <f t="shared" si="4"/>
         <v>20744</v>
       </c>
       <c r="E37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20388</v>
       </c>
       <c r="F37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>20877</v>
       </c>
       <c r="G37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20740</v>
       </c>
-      <c r="H37">
-        <f t="shared" si="5"/>
+      <c r="H37" s="2">
+        <f t="shared" si="8"/>
         <v>0.98530952905286129</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I37">
+        <v>0.98530952905286129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -2139,26 +2273,30 @@
         <v>21</v>
       </c>
       <c r="D38">
+        <f t="shared" si="4"/>
         <v>20708</v>
       </c>
       <c r="E38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20358</v>
       </c>
       <c r="F38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>20839</v>
       </c>
       <c r="G38">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20706</v>
       </c>
-      <c r="H38">
-        <f t="shared" si="5"/>
+      <c r="H38" s="2">
+        <f t="shared" si="8"/>
         <v>0.79727335938628408</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I38">
+        <v>0.79727335938628408</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -2169,26 +2307,30 @@
         <v>22</v>
       </c>
       <c r="D39">
+        <f t="shared" si="4"/>
         <v>20679</v>
       </c>
       <c r="E39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20335</v>
       </c>
       <c r="F39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>20808</v>
       </c>
       <c r="G39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20678</v>
       </c>
-      <c r="H39">
-        <f t="shared" si="5"/>
+      <c r="H39" s="2">
+        <f t="shared" si="8"/>
         <v>0.64579977826598589</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I39">
+        <v>0.64579977826598589</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -2199,26 +2341,30 @@
         <v>23</v>
       </c>
       <c r="D40">
+        <f t="shared" si="4"/>
         <v>20277</v>
       </c>
       <c r="E40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20007</v>
       </c>
       <c r="F40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>20384</v>
       </c>
       <c r="G40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20294</v>
       </c>
-      <c r="H40">
-        <f t="shared" si="5"/>
+      <c r="H40" s="2">
+        <f t="shared" si="8"/>
         <v>-1.4539374496774591</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I40">
+        <v>-1.4539374496774591</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="1" customFormat="1">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -2228,28 +2374,32 @@
       <c r="C41" s="1">
         <v>24</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41">
+        <f t="shared" si="4"/>
         <v>20355</v>
       </c>
       <c r="E41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20071</v>
       </c>
       <c r="F41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>20467</v>
       </c>
       <c r="G41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20369</v>
       </c>
-      <c r="H41">
-        <f t="shared" si="5"/>
+      <c r="H41" s="2">
+        <f t="shared" si="8"/>
         <v>-1.0465257487332085</v>
       </c>
-      <c r="I41" s="3"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I41">
+        <v>-1.0465257487332085</v>
+      </c>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -2260,38 +2410,42 @@
         <v>0</v>
       </c>
       <c r="D42">
+        <f>ROUND( $I42*J$43+J$42,0)</f>
         <v>21883</v>
       </c>
       <c r="E42">
-        <f>ROUND( $H42*J$43+J$42,0)</f>
-        <v>20879</v>
+        <f>ROUND( $H42*K$43+K$42,0)</f>
+        <v>21052</v>
       </c>
       <c r="F42">
-        <f t="shared" ref="F42:G57" si="8">ROUND( $H42*K$43+K$42,0)</f>
-        <v>21974</v>
+        <f>ROUND( $H42*L$43+L$42,0)</f>
+        <v>21888</v>
       </c>
       <c r="G42">
-        <f t="shared" si="8"/>
-        <v>21519</v>
-      </c>
-      <c r="H42">
-        <f>(D42-I$42)/I$43</f>
-        <v>-0.55367752377277335</v>
-      </c>
-      <c r="I42" s="2">
-        <v>22028.864864864863</v>
+        <f>ROUND( $H42*M$43+M$42,0)</f>
+        <v>22104</v>
+      </c>
+      <c r="H42" s="2">
+        <f>(D42-J$42)/J$43</f>
+        <v>-0.17409500793832094</v>
+      </c>
+      <c r="I42">
+        <v>-0.17409500793832094</v>
       </c>
       <c r="J42" s="2">
-        <v>20985.027027027027</v>
+        <v>21928.8648648649</v>
       </c>
       <c r="K42" s="2">
-        <v>22140.432432432433</v>
+        <v>21085.027027027001</v>
       </c>
       <c r="L42" s="2">
-        <v>21642.594594594593</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+        <v>21940.432432432401</v>
+      </c>
+      <c r="M42" s="2">
+        <v>22142.5945945946</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -2302,38 +2456,42 @@
         <v>1</v>
       </c>
       <c r="D43">
+        <f t="shared" ref="D43:D78" si="11">ROUND( $I43*J$43+J$42,0)</f>
         <v>22048</v>
       </c>
       <c r="E43">
-        <f t="shared" ref="E43:E78" si="9">ROUND( $H43*J$43+J$42,0)</f>
-        <v>20999</v>
+        <f t="shared" ref="E43:E78" si="12">ROUND( $H43*K$43+K$42,0)</f>
+        <v>21172</v>
       </c>
       <c r="F43">
-        <f t="shared" si="8"/>
-        <v>22162</v>
+        <f t="shared" ref="F43:F57" si="13">ROUND( $H43*L$43+L$42,0)</f>
+        <v>22077</v>
       </c>
       <c r="G43">
-        <f t="shared" si="8"/>
-        <v>21659</v>
-      </c>
-      <c r="H43">
-        <f t="shared" ref="H43:H78" si="10">(D43-I$42)/I$43</f>
-        <v>7.2633627354300956E-2</v>
-      </c>
-      <c r="I43" s="2">
+        <f t="shared" ref="G43:G57" si="14">ROUND( $H43*M$43+M$42,0)</f>
+        <v>22243</v>
+      </c>
+      <c r="H43" s="2">
+        <f t="shared" ref="H43:H78" si="15">(D43-J$42)/J$43</f>
+        <v>0.45221614318875336</v>
+      </c>
+      <c r="I43">
+        <v>0.45221614318875336</v>
+      </c>
+      <c r="J43" s="2">
         <v>263.44732917987375</v>
       </c>
-      <c r="J43" s="2">
+      <c r="K43" s="2">
         <v>192.04088619937818</v>
       </c>
-      <c r="K43" s="2">
+      <c r="L43" s="2">
         <v>301.02918423127704</v>
       </c>
-      <c r="L43" s="2">
+      <c r="M43" s="2">
         <v>223.0065396519536</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -2344,26 +2502,30 @@
         <v>2</v>
       </c>
       <c r="D44">
+        <f t="shared" si="11"/>
         <v>22294</v>
       </c>
       <c r="E44">
-        <f t="shared" si="9"/>
-        <v>21178</v>
+        <f t="shared" si="12"/>
+        <v>21351</v>
       </c>
       <c r="F44">
-        <f t="shared" si="8"/>
-        <v>22443</v>
+        <f t="shared" si="13"/>
+        <v>22358</v>
       </c>
       <c r="G44">
-        <f t="shared" si="8"/>
-        <v>21867</v>
-      </c>
-      <c r="H44">
-        <f t="shared" si="10"/>
-        <v>1.0064066163073935</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22452</v>
+      </c>
+      <c r="H44" s="2">
+        <f t="shared" si="15"/>
+        <v>1.385989132141846</v>
+      </c>
+      <c r="I44">
+        <v>1.385989132141846</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -2374,26 +2536,46 @@
         <v>3</v>
       </c>
       <c r="D45">
+        <f t="shared" si="11"/>
         <v>22243</v>
       </c>
       <c r="E45">
-        <f t="shared" si="9"/>
-        <v>21141</v>
+        <f t="shared" si="12"/>
+        <v>21314</v>
       </c>
       <c r="F45">
-        <f t="shared" si="8"/>
-        <v>22385</v>
+        <f t="shared" si="13"/>
+        <v>22299</v>
       </c>
       <c r="G45">
-        <f t="shared" si="8"/>
-        <v>21824</v>
-      </c>
-      <c r="H45">
-        <f t="shared" si="10"/>
-        <v>0.81281953323175238</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22409</v>
+      </c>
+      <c r="H45" s="2">
+        <f t="shared" si="15"/>
+        <v>1.1924020490662048</v>
+      </c>
+      <c r="I45">
+        <v>1.1924020490662048</v>
+      </c>
+      <c r="J45" s="2">
+        <f>AVERAGE(D42:D78)</f>
+        <v>22028.864864864863</v>
+      </c>
+      <c r="K45" s="2">
+        <f t="shared" ref="K45:M45" si="16">AVERAGE(E42:E78)</f>
+        <v>21157.891891891893</v>
+      </c>
+      <c r="L45" s="2">
+        <f t="shared" si="16"/>
+        <v>22054.675675675677</v>
+      </c>
+      <c r="M45" s="2">
+        <f t="shared" si="16"/>
+        <v>22227.162162162163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -2404,26 +2586,30 @@
         <v>4</v>
       </c>
       <c r="D46">
+        <f t="shared" si="11"/>
         <v>22142</v>
       </c>
       <c r="E46">
-        <f t="shared" si="9"/>
-        <v>21067</v>
+        <f t="shared" si="12"/>
+        <v>21240</v>
       </c>
       <c r="F46">
-        <f t="shared" si="8"/>
-        <v>22270</v>
+        <f t="shared" si="13"/>
+        <v>22184</v>
       </c>
       <c r="G46">
-        <f t="shared" si="8"/>
-        <v>21738</v>
-      </c>
-      <c r="H46">
-        <f t="shared" si="10"/>
-        <v>0.42944119223881599</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22323</v>
+      </c>
+      <c r="H46" s="2">
+        <f t="shared" si="15"/>
+        <v>0.8090237080732684</v>
+      </c>
+      <c r="I46">
+        <v>0.8090237080732684</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -2434,26 +2620,30 @@
         <v>5</v>
       </c>
       <c r="D47">
+        <f t="shared" si="11"/>
         <v>21886</v>
       </c>
       <c r="E47">
-        <f t="shared" si="9"/>
-        <v>20881</v>
+        <f t="shared" si="12"/>
+        <v>21054</v>
       </c>
       <c r="F47">
-        <f t="shared" si="8"/>
-        <v>21977</v>
+        <f t="shared" si="13"/>
+        <v>21891</v>
       </c>
       <c r="G47">
-        <f t="shared" si="8"/>
-        <v>21522</v>
-      </c>
-      <c r="H47">
-        <f t="shared" si="10"/>
-        <v>-0.54229004829773564</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22106</v>
+      </c>
+      <c r="H47" s="2">
+        <f t="shared" si="15"/>
+        <v>-0.16270753246328323</v>
+      </c>
+      <c r="I47">
+        <v>-0.16270753246328323</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -2464,26 +2654,30 @@
         <v>6</v>
       </c>
       <c r="D48">
+        <f t="shared" si="11"/>
         <v>22200</v>
       </c>
       <c r="E48">
-        <f t="shared" si="9"/>
-        <v>21110</v>
+        <f t="shared" si="12"/>
+        <v>21283</v>
       </c>
       <c r="F48">
-        <f t="shared" si="8"/>
-        <v>22336</v>
+        <f t="shared" si="13"/>
+        <v>22250</v>
       </c>
       <c r="G48">
-        <f t="shared" si="8"/>
-        <v>21787</v>
-      </c>
-      <c r="H48">
-        <f t="shared" si="10"/>
-        <v>0.64959905142287855</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22372</v>
+      </c>
+      <c r="H48" s="2">
+        <f t="shared" si="15"/>
+        <v>1.029181567257331</v>
+      </c>
+      <c r="I48">
+        <v>1.029181567257331</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -2494,26 +2688,30 @@
         <v>7</v>
       </c>
       <c r="D49">
+        <f t="shared" si="11"/>
         <v>22387</v>
       </c>
       <c r="E49">
-        <f t="shared" si="9"/>
-        <v>21246</v>
+        <f t="shared" si="12"/>
+        <v>21419</v>
       </c>
       <c r="F49">
-        <f t="shared" si="8"/>
-        <v>22550</v>
+        <f t="shared" si="13"/>
+        <v>22464</v>
       </c>
       <c r="G49">
-        <f t="shared" si="8"/>
-        <v>21946</v>
-      </c>
-      <c r="H49">
-        <f t="shared" si="10"/>
-        <v>1.3594183560335626</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22530</v>
+      </c>
+      <c r="H49" s="2">
+        <f t="shared" si="15"/>
+        <v>1.7390008718680152</v>
+      </c>
+      <c r="I49">
+        <v>1.7390008718680152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -2524,26 +2722,30 @@
         <v>8</v>
       </c>
       <c r="D50">
+        <f t="shared" si="11"/>
         <v>22073</v>
       </c>
       <c r="E50">
-        <f t="shared" si="9"/>
-        <v>21017</v>
+        <f t="shared" si="12"/>
+        <v>21190</v>
       </c>
       <c r="F50">
-        <f t="shared" si="8"/>
-        <v>22191</v>
+        <f t="shared" si="13"/>
+        <v>22105</v>
       </c>
       <c r="G50">
-        <f t="shared" si="8"/>
-        <v>21680</v>
-      </c>
-      <c r="H50">
-        <f t="shared" si="10"/>
-        <v>0.16752925631294857</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22265</v>
+      </c>
+      <c r="H50" s="2">
+        <f t="shared" si="15"/>
+        <v>0.54711177214740103</v>
+      </c>
+      <c r="I50">
+        <v>0.54711177214740103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -2554,26 +2756,30 @@
         <v>9</v>
       </c>
       <c r="D51">
+        <f t="shared" si="11"/>
         <v>22167</v>
       </c>
       <c r="E51">
-        <f t="shared" si="9"/>
-        <v>21086</v>
+        <f t="shared" si="12"/>
+        <v>21259</v>
       </c>
       <c r="F51">
-        <f t="shared" si="8"/>
-        <v>22298</v>
+        <f t="shared" si="13"/>
+        <v>22213</v>
       </c>
       <c r="G51">
-        <f t="shared" si="8"/>
-        <v>21760</v>
-      </c>
-      <c r="H51">
-        <f t="shared" si="10"/>
-        <v>0.52433682119746361</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22344</v>
+      </c>
+      <c r="H51" s="2">
+        <f t="shared" si="15"/>
+        <v>0.90391933703191607</v>
+      </c>
+      <c r="I51">
+        <v>0.90391933703191607</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -2584,26 +2790,30 @@
         <v>10</v>
       </c>
       <c r="D52">
+        <f t="shared" si="11"/>
         <v>22458</v>
       </c>
       <c r="E52">
-        <f t="shared" si="9"/>
-        <v>21298</v>
+        <f t="shared" si="12"/>
+        <v>21471</v>
       </c>
       <c r="F52">
-        <f t="shared" si="8"/>
-        <v>22631</v>
+        <f t="shared" si="13"/>
+        <v>22545</v>
       </c>
       <c r="G52">
-        <f t="shared" si="8"/>
-        <v>22006</v>
-      </c>
-      <c r="H52">
-        <f t="shared" si="10"/>
-        <v>1.6289219422761219</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22591</v>
+      </c>
+      <c r="H52" s="2">
+        <f t="shared" si="15"/>
+        <v>2.0085044581105742</v>
+      </c>
+      <c r="I52">
+        <v>2.0085044581105742</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -2614,26 +2824,30 @@
         <v>11</v>
       </c>
       <c r="D53">
+        <f t="shared" si="11"/>
         <v>21928</v>
       </c>
       <c r="E53">
-        <f t="shared" si="9"/>
-        <v>20912</v>
+        <f t="shared" si="12"/>
+        <v>21084</v>
       </c>
       <c r="F53">
-        <f t="shared" si="8"/>
-        <v>22025</v>
+        <f t="shared" si="13"/>
+        <v>21939</v>
       </c>
       <c r="G53">
-        <f t="shared" si="8"/>
-        <v>21557</v>
-      </c>
-      <c r="H53">
-        <f t="shared" si="10"/>
-        <v>-0.38286539164720762</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22142</v>
+      </c>
+      <c r="H53" s="2">
+        <f t="shared" si="15"/>
+        <v>-3.2828758127552318E-3</v>
+      </c>
+      <c r="I53">
+        <v>-3.2828758127552318E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -2644,26 +2858,30 @@
         <v>12</v>
       </c>
       <c r="D54">
+        <f t="shared" si="11"/>
         <v>22387</v>
       </c>
       <c r="E54">
-        <f t="shared" si="9"/>
-        <v>21246</v>
+        <f t="shared" si="12"/>
+        <v>21419</v>
       </c>
       <c r="F54">
-        <f t="shared" si="8"/>
-        <v>22550</v>
+        <f t="shared" si="13"/>
+        <v>22464</v>
       </c>
       <c r="G54">
-        <f t="shared" si="8"/>
-        <v>21946</v>
-      </c>
-      <c r="H54">
-        <f t="shared" si="10"/>
-        <v>1.3594183560335626</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22530</v>
+      </c>
+      <c r="H54" s="2">
+        <f t="shared" si="15"/>
+        <v>1.7390008718680152</v>
+      </c>
+      <c r="I54">
+        <v>1.7390008718680152</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -2674,26 +2892,30 @@
         <v>13</v>
       </c>
       <c r="D55">
+        <f t="shared" si="11"/>
         <v>22205</v>
       </c>
       <c r="E55">
-        <f t="shared" si="9"/>
-        <v>21113</v>
+        <f t="shared" si="12"/>
+        <v>21286</v>
       </c>
       <c r="F55">
-        <f t="shared" si="8"/>
-        <v>22342</v>
+        <f t="shared" si="13"/>
+        <v>22256</v>
       </c>
       <c r="G55">
-        <f t="shared" si="8"/>
-        <v>21792</v>
-      </c>
-      <c r="H55">
-        <f t="shared" si="10"/>
-        <v>0.66857817721460799</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22376</v>
+      </c>
+      <c r="H55" s="2">
+        <f t="shared" si="15"/>
+        <v>1.0481606930490603</v>
+      </c>
+      <c r="I55">
+        <v>1.0481606930490603</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -2704,26 +2926,30 @@
         <v>14</v>
       </c>
       <c r="D56">
+        <f t="shared" si="11"/>
         <v>21364</v>
       </c>
       <c r="E56">
-        <f t="shared" si="9"/>
-        <v>20500</v>
+        <f t="shared" si="12"/>
+        <v>20673</v>
       </c>
       <c r="F56">
-        <f t="shared" si="8"/>
-        <v>21381</v>
+        <f t="shared" si="13"/>
+        <v>21295</v>
       </c>
       <c r="G56">
-        <f t="shared" si="8"/>
-        <v>21080</v>
-      </c>
-      <c r="H56">
-        <f t="shared" si="10"/>
-        <v>-2.523710780954298</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>21664</v>
+      </c>
+      <c r="H56" s="2">
+        <f t="shared" si="15"/>
+        <v>-2.1441282651198454</v>
+      </c>
+      <c r="I56">
+        <v>-2.1441282651198454</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -2734,26 +2960,30 @@
         <v>15</v>
       </c>
       <c r="D57">
+        <f t="shared" si="11"/>
         <v>21970</v>
       </c>
       <c r="E57">
-        <f t="shared" si="9"/>
-        <v>20942</v>
+        <f t="shared" si="12"/>
+        <v>21115</v>
       </c>
       <c r="F57">
-        <f t="shared" si="8"/>
-        <v>22073</v>
+        <f t="shared" si="13"/>
+        <v>21987</v>
       </c>
       <c r="G57">
-        <f t="shared" si="8"/>
-        <v>21593</v>
-      </c>
-      <c r="H57">
-        <f t="shared" si="10"/>
-        <v>-0.22344073499667963</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>22177</v>
+      </c>
+      <c r="H57" s="2">
+        <f t="shared" si="15"/>
+        <v>0.15614178083777278</v>
+      </c>
+      <c r="I57">
+        <v>0.15614178083777278</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -2764,26 +2994,30 @@
         <v>16</v>
       </c>
       <c r="D58">
+        <f t="shared" si="11"/>
         <v>21642</v>
       </c>
       <c r="E58">
-        <f t="shared" si="9"/>
-        <v>20703</v>
+        <f t="shared" si="12"/>
+        <v>20876</v>
       </c>
       <c r="F58">
-        <f t="shared" ref="F58:F78" si="11">ROUND( $H58*K$43+K$42,0)</f>
-        <v>21698</v>
+        <f t="shared" ref="F58:F78" si="17">ROUND( $H58*L$43+L$42,0)</f>
+        <v>21613</v>
       </c>
       <c r="G58">
-        <f t="shared" ref="G58:G78" si="12">ROUND( $H58*L$43+L$42,0)</f>
-        <v>21315</v>
-      </c>
-      <c r="H58">
-        <f t="shared" si="10"/>
-        <v>-1.4684713869341364</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" ref="G58:G78" si="18">ROUND( $H58*M$43+M$42,0)</f>
+        <v>21900</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="15"/>
+        <v>-1.088888871099684</v>
+      </c>
+      <c r="I58">
+        <v>-1.088888871099684</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -2794,26 +3028,30 @@
         <v>17</v>
       </c>
       <c r="D59">
+        <f t="shared" si="11"/>
         <v>21601</v>
       </c>
       <c r="E59">
-        <f t="shared" si="9"/>
-        <v>20673</v>
+        <f t="shared" si="12"/>
+        <v>20846</v>
       </c>
       <c r="F59">
-        <f t="shared" si="11"/>
-        <v>21652</v>
+        <f t="shared" si="17"/>
+        <v>21566</v>
       </c>
       <c r="G59">
-        <f t="shared" si="12"/>
-        <v>21280</v>
-      </c>
-      <c r="H59">
-        <f t="shared" si="10"/>
-        <v>-1.6241002184263185</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>21865</v>
+      </c>
+      <c r="H59" s="2">
+        <f t="shared" si="15"/>
+        <v>-1.2445177025918661</v>
+      </c>
+      <c r="I59">
+        <v>-1.2445177025918661</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -2824,26 +3062,30 @@
         <v>18</v>
       </c>
       <c r="D60">
+        <f t="shared" si="11"/>
         <v>21873</v>
       </c>
       <c r="E60">
-        <f t="shared" si="9"/>
-        <v>20871</v>
+        <f t="shared" si="12"/>
+        <v>21044</v>
       </c>
       <c r="F60">
-        <f t="shared" si="11"/>
-        <v>21962</v>
+        <f t="shared" si="17"/>
+        <v>21877</v>
       </c>
       <c r="G60">
-        <f t="shared" si="12"/>
-        <v>21511</v>
-      </c>
-      <c r="H60">
-        <f t="shared" si="10"/>
-        <v>-0.59163577535623235</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22095</v>
+      </c>
+      <c r="H60" s="2">
+        <f t="shared" si="15"/>
+        <v>-0.21205325952178</v>
+      </c>
+      <c r="I60">
+        <v>-0.21205325952178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -2854,26 +3096,30 @@
         <v>19</v>
       </c>
       <c r="D61">
+        <f t="shared" si="11"/>
         <v>22152</v>
       </c>
       <c r="E61">
-        <f t="shared" si="9"/>
-        <v>21075</v>
+        <f t="shared" si="12"/>
+        <v>21248</v>
       </c>
       <c r="F61">
-        <f t="shared" si="11"/>
-        <v>22281</v>
+        <f t="shared" si="17"/>
+        <v>22195</v>
       </c>
       <c r="G61">
-        <f t="shared" si="12"/>
-        <v>21747</v>
-      </c>
-      <c r="H61">
-        <f t="shared" si="10"/>
-        <v>0.46739944382227505</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22331</v>
+      </c>
+      <c r="H61" s="2">
+        <f t="shared" si="15"/>
+        <v>0.84698195965672751</v>
+      </c>
+      <c r="I61">
+        <v>0.84698195965672751</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -2884,26 +3130,30 @@
         <v>20</v>
       </c>
       <c r="D62">
+        <f t="shared" si="11"/>
         <v>21589</v>
       </c>
       <c r="E62">
-        <f t="shared" si="9"/>
-        <v>20664</v>
+        <f t="shared" si="12"/>
+        <v>20837</v>
       </c>
       <c r="F62">
-        <f t="shared" si="11"/>
-        <v>21638</v>
+        <f t="shared" si="17"/>
+        <v>21552</v>
       </c>
       <c r="G62">
-        <f t="shared" si="12"/>
-        <v>21270</v>
-      </c>
-      <c r="H62">
-        <f t="shared" si="10"/>
-        <v>-1.6696501203264693</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>21855</v>
+      </c>
+      <c r="H62" s="2">
+        <f t="shared" si="15"/>
+        <v>-1.290067604492017</v>
+      </c>
+      <c r="I62">
+        <v>-1.290067604492017</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -2914,26 +3164,30 @@
         <v>21</v>
       </c>
       <c r="D63">
+        <f t="shared" si="11"/>
         <v>21825</v>
       </c>
       <c r="E63">
-        <f t="shared" si="9"/>
-        <v>20836</v>
+        <f t="shared" si="12"/>
+        <v>21009</v>
       </c>
       <c r="F63">
-        <f t="shared" si="11"/>
-        <v>21907</v>
+        <f t="shared" si="17"/>
+        <v>21822</v>
       </c>
       <c r="G63">
-        <f t="shared" si="12"/>
-        <v>21470</v>
-      </c>
-      <c r="H63">
-        <f t="shared" si="10"/>
-        <v>-0.77383538295683585</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22055</v>
+      </c>
+      <c r="H63" s="2">
+        <f t="shared" si="15"/>
+        <v>-0.39425286712238344</v>
+      </c>
+      <c r="I63">
+        <v>-0.39425286712238344</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -2944,26 +3198,30 @@
         <v>22</v>
       </c>
       <c r="D64">
+        <f t="shared" si="11"/>
         <v>21901</v>
       </c>
       <c r="E64">
-        <f t="shared" si="9"/>
-        <v>20892</v>
+        <f t="shared" si="12"/>
+        <v>21065</v>
       </c>
       <c r="F64">
-        <f t="shared" si="11"/>
-        <v>21994</v>
+        <f t="shared" si="17"/>
+        <v>21909</v>
       </c>
       <c r="G64">
-        <f t="shared" si="12"/>
-        <v>21534</v>
-      </c>
-      <c r="H64">
-        <f t="shared" si="10"/>
-        <v>-0.48535267092254708</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22119</v>
+      </c>
+      <c r="H64" s="2">
+        <f t="shared" si="15"/>
+        <v>-0.10577015508809466</v>
+      </c>
+      <c r="I64">
+        <v>-0.10577015508809466</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>7</v>
       </c>
@@ -2974,26 +3232,30 @@
         <v>23</v>
       </c>
       <c r="D65">
+        <f t="shared" si="11"/>
         <v>22169</v>
       </c>
       <c r="E65">
-        <f t="shared" si="9"/>
-        <v>21087</v>
+        <f t="shared" si="12"/>
+        <v>21260</v>
       </c>
       <c r="F65">
-        <f t="shared" si="11"/>
-        <v>22301</v>
+        <f t="shared" si="17"/>
+        <v>22215</v>
       </c>
       <c r="G65">
-        <f t="shared" si="12"/>
-        <v>21761</v>
-      </c>
-      <c r="H65">
-        <f t="shared" si="10"/>
-        <v>0.53192847151415545</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22346</v>
+      </c>
+      <c r="H65" s="2">
+        <f t="shared" si="15"/>
+        <v>0.9115109873486078</v>
+      </c>
+      <c r="I65">
+        <v>0.9115109873486078</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
         <v>7</v>
       </c>
@@ -3004,26 +3266,30 @@
         <v>24</v>
       </c>
       <c r="D66">
+        <f t="shared" si="11"/>
         <v>21779</v>
       </c>
       <c r="E66">
-        <f t="shared" si="9"/>
-        <v>20803</v>
+        <f t="shared" si="12"/>
+        <v>20976</v>
       </c>
       <c r="F66">
-        <f t="shared" si="11"/>
-        <v>21855</v>
+        <f t="shared" si="17"/>
+        <v>21769</v>
       </c>
       <c r="G66">
-        <f t="shared" si="12"/>
-        <v>21431</v>
-      </c>
-      <c r="H66">
-        <f t="shared" si="10"/>
-        <v>-0.9484433402407475</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22016</v>
+      </c>
+      <c r="H66" s="2">
+        <f t="shared" si="15"/>
+        <v>-0.56886082440629504</v>
+      </c>
+      <c r="I66">
+        <v>-0.56886082440629504</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
         <v>7</v>
       </c>
@@ -3034,26 +3300,30 @@
         <v>25</v>
       </c>
       <c r="D67">
+        <f t="shared" si="11"/>
         <v>21893</v>
       </c>
       <c r="E67">
-        <f t="shared" si="9"/>
-        <v>20886</v>
+        <f t="shared" si="12"/>
+        <v>21059</v>
       </c>
       <c r="F67">
-        <f t="shared" si="11"/>
-        <v>21985</v>
+        <f t="shared" si="17"/>
+        <v>21899</v>
       </c>
       <c r="G67">
-        <f t="shared" si="12"/>
-        <v>21528</v>
-      </c>
-      <c r="H67">
-        <f t="shared" si="10"/>
-        <v>-0.51571927218931435</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22112</v>
+      </c>
+      <c r="H67" s="2">
+        <f t="shared" si="15"/>
+        <v>-0.13613675635486192</v>
+      </c>
+      <c r="I67">
+        <v>-0.13613675635486192</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
         <v>7</v>
       </c>
@@ -3064,26 +3334,30 @@
         <v>26</v>
       </c>
       <c r="D68">
+        <f t="shared" si="11"/>
         <v>21983</v>
       </c>
       <c r="E68">
-        <f t="shared" si="9"/>
-        <v>20952</v>
+        <f t="shared" si="12"/>
+        <v>21124</v>
       </c>
       <c r="F68">
-        <f t="shared" si="11"/>
-        <v>22088</v>
+        <f t="shared" si="17"/>
+        <v>22002</v>
       </c>
       <c r="G68">
-        <f t="shared" si="12"/>
-        <v>21604</v>
-      </c>
-      <c r="H68">
-        <f t="shared" si="10"/>
-        <v>-0.17409500793818286</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22188</v>
+      </c>
+      <c r="H68" s="2">
+        <f t="shared" si="15"/>
+        <v>0.20548750789626954</v>
+      </c>
+      <c r="I68">
+        <v>0.20548750789626954</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -3094,26 +3368,30 @@
         <v>27</v>
       </c>
       <c r="D69">
+        <f t="shared" si="11"/>
         <v>22166</v>
       </c>
       <c r="E69">
-        <f t="shared" si="9"/>
-        <v>21085</v>
+        <f t="shared" si="12"/>
+        <v>21258</v>
       </c>
       <c r="F69">
-        <f t="shared" si="11"/>
-        <v>22297</v>
+        <f t="shared" si="17"/>
+        <v>22211</v>
       </c>
       <c r="G69">
-        <f t="shared" si="12"/>
-        <v>21759</v>
-      </c>
-      <c r="H69">
-        <f t="shared" si="10"/>
-        <v>0.52054099603911774</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22343</v>
+      </c>
+      <c r="H69" s="2">
+        <f t="shared" si="15"/>
+        <v>0.90012351187357009</v>
+      </c>
+      <c r="I69">
+        <v>0.90012351187357009</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -3124,26 +3402,30 @@
         <v>28</v>
       </c>
       <c r="D70">
+        <f t="shared" si="11"/>
         <v>22682</v>
       </c>
       <c r="E70">
-        <f t="shared" si="9"/>
-        <v>21461</v>
+        <f t="shared" si="12"/>
+        <v>21634</v>
       </c>
       <c r="F70">
-        <f t="shared" si="11"/>
-        <v>22887</v>
+        <f t="shared" si="17"/>
+        <v>22801</v>
       </c>
       <c r="G70">
-        <f t="shared" si="12"/>
-        <v>22195</v>
-      </c>
-      <c r="H70">
-        <f t="shared" si="10"/>
-        <v>2.4791867777456047</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22780</v>
+      </c>
+      <c r="H70" s="2">
+        <f t="shared" si="15"/>
+        <v>2.8587692935800573</v>
+      </c>
+      <c r="I70">
+        <v>2.8587692935800573</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
         <v>7</v>
       </c>
@@ -3154,26 +3436,30 @@
         <v>29</v>
       </c>
       <c r="D71">
+        <f t="shared" si="11"/>
         <v>21911</v>
       </c>
       <c r="E71">
-        <f t="shared" si="9"/>
-        <v>20899</v>
+        <f t="shared" si="12"/>
+        <v>21072</v>
       </c>
       <c r="F71">
-        <f t="shared" si="11"/>
-        <v>22006</v>
+        <f t="shared" si="17"/>
+        <v>21920</v>
       </c>
       <c r="G71">
-        <f t="shared" si="12"/>
-        <v>21543</v>
-      </c>
-      <c r="H71">
-        <f t="shared" si="10"/>
-        <v>-0.44739441933908802</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22127</v>
+      </c>
+      <c r="H71" s="2">
+        <f t="shared" si="15"/>
+        <v>-6.7811903504635618E-2</v>
+      </c>
+      <c r="I71">
+        <v>-6.7811903504635618E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
         <v>7</v>
       </c>
@@ -3184,26 +3470,30 @@
         <v>30</v>
       </c>
       <c r="D72">
+        <f t="shared" si="11"/>
         <v>22200</v>
       </c>
       <c r="E72">
-        <f t="shared" si="9"/>
-        <v>21110</v>
+        <f t="shared" si="12"/>
+        <v>21283</v>
       </c>
       <c r="F72">
-        <f t="shared" si="11"/>
-        <v>22336</v>
+        <f t="shared" si="17"/>
+        <v>22250</v>
       </c>
       <c r="G72">
-        <f t="shared" si="12"/>
-        <v>21787</v>
-      </c>
-      <c r="H72">
-        <f t="shared" si="10"/>
-        <v>0.64959905142287855</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22372</v>
+      </c>
+      <c r="H72" s="2">
+        <f t="shared" si="15"/>
+        <v>1.029181567257331</v>
+      </c>
+      <c r="I72">
+        <v>1.029181567257331</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
         <v>7</v>
       </c>
@@ -3214,26 +3504,30 @@
         <v>31</v>
       </c>
       <c r="D73">
+        <f t="shared" si="11"/>
         <v>22143</v>
       </c>
       <c r="E73">
-        <f t="shared" si="9"/>
-        <v>21068</v>
+        <f t="shared" si="12"/>
+        <v>21241</v>
       </c>
       <c r="F73">
-        <f t="shared" si="11"/>
-        <v>22271</v>
+        <f t="shared" si="17"/>
+        <v>22185</v>
       </c>
       <c r="G73">
-        <f t="shared" si="12"/>
-        <v>21739</v>
-      </c>
-      <c r="H73">
-        <f t="shared" si="10"/>
-        <v>0.43323701739716192</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22324</v>
+      </c>
+      <c r="H73" s="2">
+        <f t="shared" si="15"/>
+        <v>0.81281953323161427</v>
+      </c>
+      <c r="I73">
+        <v>0.81281953323161427</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
         <v>7</v>
       </c>
@@ -3244,26 +3538,30 @@
         <v>32</v>
       </c>
       <c r="D74">
+        <f t="shared" si="11"/>
         <v>21968</v>
       </c>
       <c r="E74">
-        <f t="shared" si="9"/>
-        <v>20941</v>
+        <f t="shared" si="12"/>
+        <v>21114</v>
       </c>
       <c r="F74">
-        <f t="shared" si="11"/>
-        <v>22071</v>
+        <f t="shared" si="17"/>
+        <v>21985</v>
       </c>
       <c r="G74">
-        <f t="shared" si="12"/>
-        <v>21591</v>
-      </c>
-      <c r="H74">
-        <f t="shared" si="10"/>
-        <v>-0.23103238531337145</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22176</v>
+      </c>
+      <c r="H74" s="2">
+        <f t="shared" si="15"/>
+        <v>0.14855013052108096</v>
+      </c>
+      <c r="I74">
+        <v>0.14855013052108096</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -3274,26 +3572,30 @@
         <v>33</v>
       </c>
       <c r="D75">
+        <f t="shared" si="11"/>
         <v>21622</v>
       </c>
       <c r="E75">
-        <f t="shared" si="9"/>
-        <v>20688</v>
+        <f t="shared" si="12"/>
+        <v>20861</v>
       </c>
       <c r="F75">
-        <f t="shared" si="11"/>
-        <v>21676</v>
+        <f t="shared" si="17"/>
+        <v>21590</v>
       </c>
       <c r="G75">
-        <f t="shared" si="12"/>
-        <v>21298</v>
-      </c>
-      <c r="H75">
-        <f t="shared" si="10"/>
-        <v>-1.5443878901010546</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>21883</v>
+      </c>
+      <c r="H75" s="2">
+        <f t="shared" si="15"/>
+        <v>-1.164805374266602</v>
+      </c>
+      <c r="I75">
+        <v>-1.164805374266602</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
         <v>7</v>
       </c>
@@ -3304,26 +3606,30 @@
         <v>34</v>
       </c>
       <c r="D76">
+        <f t="shared" si="11"/>
         <v>22146</v>
       </c>
       <c r="E76">
-        <f t="shared" si="9"/>
-        <v>21070</v>
+        <f t="shared" si="12"/>
+        <v>21243</v>
       </c>
       <c r="F76">
-        <f t="shared" si="11"/>
-        <v>22274</v>
+        <f t="shared" si="17"/>
+        <v>22189</v>
       </c>
       <c r="G76">
-        <f t="shared" si="12"/>
-        <v>21742</v>
-      </c>
-      <c r="H76">
-        <f t="shared" si="10"/>
-        <v>0.44462449287219963</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22326</v>
+      </c>
+      <c r="H76" s="2">
+        <f t="shared" si="15"/>
+        <v>0.82420700870665209</v>
+      </c>
+      <c r="I76">
+        <v>0.82420700870665209</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
         <v>7</v>
       </c>
@@ -3334,26 +3640,30 @@
         <v>34</v>
       </c>
       <c r="D77">
+        <f t="shared" si="11"/>
         <v>22094</v>
       </c>
       <c r="E77">
-        <f t="shared" si="9"/>
-        <v>21033</v>
+        <f t="shared" si="12"/>
+        <v>21205</v>
       </c>
       <c r="F77">
-        <f t="shared" si="11"/>
-        <v>22215</v>
+        <f t="shared" si="17"/>
+        <v>22129</v>
       </c>
       <c r="G77">
-        <f t="shared" si="12"/>
-        <v>21698</v>
-      </c>
-      <c r="H77">
-        <f t="shared" si="10"/>
-        <v>0.24724158463821258</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>22282</v>
+      </c>
+      <c r="H77" s="2">
+        <f t="shared" si="15"/>
+        <v>0.62682410047266501</v>
+      </c>
+      <c r="I77">
+        <v>0.62682410047266501</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -3364,23 +3674,27 @@
         <v>34</v>
       </c>
       <c r="D78">
+        <f t="shared" si="11"/>
         <v>22094</v>
       </c>
       <c r="E78">
-        <f t="shared" si="9"/>
-        <v>21033</v>
+        <f t="shared" si="12"/>
+        <v>21205</v>
       </c>
       <c r="F78">
-        <f t="shared" si="11"/>
-        <v>22215</v>
+        <f t="shared" si="17"/>
+        <v>22129</v>
       </c>
       <c r="G78">
-        <f t="shared" si="12"/>
-        <v>21698</v>
-      </c>
-      <c r="H78">
-        <f t="shared" si="10"/>
-        <v>0.24724158463821258</v>
+        <f t="shared" si="18"/>
+        <v>22282</v>
+      </c>
+      <c r="H78" s="2">
+        <f t="shared" si="15"/>
+        <v>0.62682410047266501</v>
+      </c>
+      <c r="I78">
+        <v>0.62682410047266501</v>
       </c>
     </row>
   </sheetData>
